--- a/server/data/xlsx/Enums.xlsx
+++ b/server/data/xlsx/Enums.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col width="13.28515625" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
@@ -951,91 +951,209 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
         <is>
           <t>EnumName</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="0" t="inlineStr">
         <is>
           <t>ObjectType</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="0" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="0" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="0" t="inlineStr">
         <is>
           <t>DungeonPortal</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr">
         <is>
           <t>던전 입장 포탈</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
         <is>
           <t>Npc</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="0" t="inlineStr">
         <is>
           <t>NPC</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="0" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
         <is>
           <t>상점</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="0" t="inlineStr">
         <is>
           <t>QuestBoard</t>
         </is>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="0" t="inlineStr">
         <is>
           <t>퀘스트 게시판</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="inlineStr">
+        <is>
+          <t>EnumName</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="inlineStr">
+        <is>
+          <t>DungeonType</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B46" s="0" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="inlineStr">
+        <is>
+          <t>KillAll</t>
+        </is>
+      </c>
+      <c r="B47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="0" t="inlineStr">
+        <is>
+          <t>몬스터 전멸 클리어</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="inlineStr">
+        <is>
+          <t>Timed</t>
+        </is>
+      </c>
+      <c r="B48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t>제한시간 생존 클리어</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>EnumName</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>DungeonType</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>KillAll</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>몬스터 전멸 클리어</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Timed</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>제한시간 클리어</t>
         </is>
       </c>
     </row>

--- a/server/data/xlsx/Enums.xlsx
+++ b/server/data/xlsx/Enums.xlsx
@@ -469,691 +469,744 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col width="13.28515625" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>EnumName</t>
         </is>
       </c>
-      <c r="B1" s="0" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>MonsterType</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B2" s="0" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C2" s="0" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" t="n">
         <v>0</v>
       </c>
-      <c r="C3" s="0" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>일반 몬스터</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Elite</t>
         </is>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="0" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>엘리트 몬스터</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="0" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>보스 몬스터</t>
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>EnumName</t>
         </is>
       </c>
-      <c r="B7" s="0" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>ItemGradeType</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B8" s="0" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C8" s="0" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="0" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="0" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>레어</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="0" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>에픽</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="0" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>전설</t>
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
-      <c r="A14" s="0" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>EnumName</t>
         </is>
       </c>
-      <c r="B14" s="0" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>SkillType</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="0" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B15" s="0" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C15" s="0" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="0" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>AttackMelee</t>
         </is>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" t="n">
         <v>0</v>
       </c>
-      <c r="C16" s="0" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>근거리 물리 공격</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="0" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>AttackRanged</t>
         </is>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="0" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>원거리 물리 공격</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="0" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>AttackMagic</t>
         </is>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="0" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>마법 공격</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="0" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="0" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>버프</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="0" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Debuff</t>
         </is>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" t="n">
         <v>4</v>
       </c>
-      <c r="C20" s="0" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>디버프</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="0" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Heal</t>
         </is>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21" t="n">
         <v>5</v>
       </c>
-      <c r="C21" s="0" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>회복</t>
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
-      <c r="A23" s="0" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>EnumName</t>
         </is>
       </c>
-      <c r="B23" s="0" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>ItemRarity</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="0" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B24" s="0" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C24" s="0" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="0" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="0" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="0" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" t="n">
         <v>1</v>
       </c>
-      <c r="C26" s="0" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>레어</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="0" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" t="n">
         <v>2</v>
       </c>
-      <c r="C27" s="0" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>에픽</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="0" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="B28" s="0" t="n">
+      <c r="B28" t="n">
         <v>3</v>
       </c>
-      <c r="C28" s="0" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>전설</t>
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
-      <c r="A30" s="0" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>EnumName</t>
         </is>
       </c>
-      <c r="B30" s="0" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>CharacterType</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="0" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B31" s="0" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C31" s="0" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="0" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Tank</t>
         </is>
       </c>
-      <c r="B32" s="0" t="n">
+      <c r="B32" t="n">
         <v>0</v>
       </c>
-      <c r="C32" s="0" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>방어 — 높은 HP/방어, 어그로 유지</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="0" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Melee</t>
         </is>
       </c>
-      <c r="B33" s="0" t="n">
+      <c r="B33" t="n">
         <v>1</v>
       </c>
-      <c r="C33" s="0" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>근거리 공격</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="0" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Ranged</t>
         </is>
       </c>
-      <c r="B34" s="0" t="n">
+      <c r="B34" t="n">
         <v>2</v>
       </c>
-      <c r="C34" s="0" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>원거리 공격</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="0" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Magic</t>
         </is>
       </c>
-      <c r="B35" s="0" t="n">
+      <c r="B35" t="n">
         <v>3</v>
       </c>
-      <c r="C35" s="0" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>마법 딜러</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="0" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="B36" s="0" t="n">
+      <c r="B36" t="n">
         <v>4</v>
       </c>
-      <c r="C36" s="0" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>지원 — 힐, 버프</t>
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
-      <c r="A38" s="0" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>EnumName</t>
         </is>
       </c>
-      <c r="B38" s="0" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>ObjectType</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="0" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B39" s="0" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C39" s="0" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="0" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>DungeonPortal</t>
         </is>
       </c>
-      <c r="B40" s="0" t="n">
+      <c r="B40" t="n">
         <v>0</v>
       </c>
-      <c r="C40" s="0" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>던전 입장 포탈</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="0" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Npc</t>
         </is>
       </c>
-      <c r="B41" s="0" t="n">
+      <c r="B41" t="n">
         <v>1</v>
       </c>
-      <c r="C41" s="0" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>NPC</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="0" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Shop</t>
         </is>
       </c>
-      <c r="B42" s="0" t="n">
+      <c r="B42" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="0" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>상점</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="0" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>QuestBoard</t>
         </is>
       </c>
-      <c r="B43" s="0" t="n">
+      <c r="B43" t="n">
         <v>3</v>
       </c>
-      <c r="C43" s="0" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>퀘스트 게시판</t>
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>FieldPortal</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>4</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>시간제 사냥터 포탈</t>
+        </is>
+      </c>
+    </row>
     <row r="45">
-      <c r="A45" s="0" t="inlineStr">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Collectible</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>5</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>채집 오브젝트</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>EnumName</t>
         </is>
       </c>
-      <c r="B45" s="0" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>DungeonType</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="0" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B46" s="0" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C46" s="0" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="0" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>KillAll</t>
         </is>
       </c>
-      <c r="B47" s="0" t="n">
+      <c r="B49" t="n">
         <v>0</v>
       </c>
-      <c r="C47" s="0" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>몬스터 전멸 클리어</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="0" t="inlineStr">
-        <is>
-          <t>Timed</t>
-        </is>
-      </c>
-      <c r="B48" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" s="0" t="inlineStr">
-        <is>
-          <t>제한시간 생존 클리어</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EnumName</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>DungeonType</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>KillAll</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>0</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>몬스터 전멸 클리어</t>
-        </is>
-      </c>
-    </row>
+          <t>Timed</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>제한시간 생존 클리어</t>
+        </is>
+      </c>
+    </row>
+    <row r="51"/>
+    <row r="52"/>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Timed</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
+          <t>EnumName</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>WorldObjectState</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>채집 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Harvested</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
         <v>1</v>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>제한시간 클리어</t>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>채집됨 (사라짐)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Respawning</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>2</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>리스폰 대기 중</t>
         </is>
       </c>
     </row>
